--- a/generador/plantillas/MA/C02-0001.xlsx
+++ b/generador/plantillas/MA/C02-0001.xlsx
@@ -2519,7 +2519,7 @@
       </c>
       <c r="B53" s="158" t="inlineStr">
         <is>
-          <t>CAPTEEC CENTRO DE CAPACITACIÓN TÉCNICA - EMPRESARIAL &amp; TUTORIAS S.A.S.</t>
+          <t xml:space="preserve">{{EDU_LECTO_INSTITUCION}}</t>
         </is>
       </c>
       <c r="C53" s="100" t="n"/>
@@ -2529,15 +2529,19 @@
       <c r="G53" s="99" t="n"/>
       <c r="H53" s="158" t="inlineStr">
         <is>
-          <t xml:space="preserve">ECUADOR </t>
+          <t xml:space="preserve">{{EDU_LECTO_PAIS}}</t>
         </is>
       </c>
       <c r="I53" s="158" t="inlineStr">
         <is>
-          <t>LA TRONCAL</t>
-        </is>
-      </c>
-      <c r="J53" s="158" t="n"/>
+          <t xml:space="preserve">{{EDU_LECTO_CIUDAD}}</t>
+        </is>
+      </c>
+      <c r="J53" s="158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{EDU_LECTO_TITULO}}</t>
+        </is>
+      </c>
       <c r="K53" s="100" t="n"/>
       <c r="L53" s="100" t="n"/>
       <c r="M53" s="99" t="n"/>
